--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.226727025265229</v>
+        <v>1.1743431416056</v>
       </c>
       <c r="D2" t="n">
-        <v>5.43126220493216</v>
+        <v>0.882580108301476</v>
       </c>
       <c r="E2" t="n">
-        <v>18.47139071079768</v>
+        <v>3.001600990504623</v>
       </c>
       <c r="F2" t="n">
-        <v>17.58547365193391</v>
+        <v>2.857639468439259</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.33688737328288</v>
+        <v>8.50474419815847</v>
       </c>
       <c r="D3" t="n">
-        <v>48.42469562185937</v>
+        <v>7.869013038552148</v>
       </c>
       <c r="E3" t="n">
-        <v>18.47139071079768</v>
+        <v>3.001600990504623</v>
       </c>
       <c r="F3" t="n">
-        <v>17.58547365193391</v>
+        <v>2.857639468439259</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.81005943304584</v>
+        <v>5.331634657869949</v>
       </c>
       <c r="D4" t="n">
-        <v>24.6272207120495</v>
+        <v>4.001923365708045</v>
       </c>
       <c r="E4" t="n">
-        <v>18.47139071079768</v>
+        <v>3.001600990504623</v>
       </c>
       <c r="F4" t="n">
-        <v>17.58547365193391</v>
+        <v>2.857639468439259</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
